--- a/JsonConverter/ExcelFiles/Character.xlsx
+++ b/JsonConverter/ExcelFiles/Character.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30117"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30128"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0_NRUnityProjects\UnityBasic_6\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{93C4AC31-589A-4AAD-898D-1448E48F9FD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6A26FF07-94DD-40E9-B342-5418095F7219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="4294939940" windowHeight="16840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
+    <sheet name="Character" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="44">
   <si>
     <t>캐릭터 고유 ID</t>
   </si>
@@ -50,7 +50,25 @@
     <t>캐릭터의 프리팹 경로</t>
   </si>
   <si>
-    <t>캐릭터의 도감용 정보</t>
+    <t>캐릭터의 기본 정보</t>
+  </si>
+  <si>
+    <t>해금되는 주요 정보</t>
+  </si>
+  <si>
+    <t>대화 시 기본 초상화</t>
+  </si>
+  <si>
+    <t>호감도 낮을 시 기본 초상화</t>
+  </si>
+  <si>
+    <t>호감도 높을 시 기본 초상화</t>
+  </si>
+  <si>
+    <t>건강 낮을 시 기본 초상화</t>
+  </si>
+  <si>
+    <t>멘탈 낮을 시 기본 초상화</t>
   </si>
   <si>
     <t>(name)</t>
@@ -71,29 +89,97 @@
     <t>PrefabPath</t>
   </si>
   <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>char_testNPC</t>
-  </si>
-  <si>
-    <t>NPC</t>
-  </si>
-  <si>
-    <t>Sprites/portraitnormal</t>
-  </si>
-  <si>
-    <t>Prefabs/testNPC</t>
-  </si>
-  <si>
-    <t>테스트용 NPC이다.</t>
+    <t>CharacterFileData1</t>
+  </si>
+  <si>
+    <t>CharacterFileData2</t>
+  </si>
+  <si>
+    <t>CharacterFileData3</t>
+  </si>
+  <si>
+    <t>CharacterFileData4</t>
+  </si>
+  <si>
+    <t>DialoguePortraitDefault</t>
+  </si>
+  <si>
+    <t>DialoguePortraitHateDefault</t>
+  </si>
+  <si>
+    <t>DialoguePortraitLikeDefault</t>
+  </si>
+  <si>
+    <t>DialoguePortraitSickDefault</t>
+  </si>
+  <si>
+    <t>DialoguePortraitMadnessDefault</t>
+  </si>
+  <si>
+    <t>char_girl</t>
+  </si>
+  <si>
+    <t>윤하린</t>
+  </si>
+  <si>
+    <t>Portraits/Girl_Portrait_Default|Profile</t>
+  </si>
+  <si>
+    <t>Prefabs/NPCs/NPC_Girl</t>
+  </si>
+  <si>
+    <t>변이체의 폭주에서 살아남은 유일한 연구원.
+사건의 후유증 때문인지 말주변이 없고 사람을 두려워한다.
+낮에는 거의 숙소에 틀어박혀 있어서 저녁에 주로 볼 수 있다.
+그런 끔찍한 일을 겪고도 자진해서 연구를 계속하다니
+어쩌면 생각보다 멘탈이 좋은 사람인지도 모른다.</t>
+  </si>
+  <si>
+    <t>말주면이 없고 덜렁거리는 성격은 사건의 후유증 때문이 아니었다.
+그냥 원래부터 성격이 좀 그런 사람이었다...</t>
+  </si>
+  <si>
+    <t>사실 이 작품을 처음 구상할 때 하린이라는 캐릭터는 존재하지 않았다. 하지만 벌레 괴물과 대화하며 호감도 관리까지 해줘야 하는 비주얼노벨 게임에 여주인공 포지션의 캐릭터가 존재하지 않는다면 작품이 폭삭 망할 것 같아서 스토리를 게임용으로 재구성하면서 급하게 추가한 캐릭터다.</t>
+  </si>
+  <si>
+    <t>Portraits/Girl_Portrait_Default</t>
+  </si>
+  <si>
+    <t>Portraits/Girl_Portrait_HateDefault</t>
+  </si>
+  <si>
+    <t>Portraits/Girl_Portrait_LikeDefault</t>
+  </si>
+  <si>
+    <t>char_pilot</t>
+  </si>
+  <si>
+    <t>군인</t>
+  </si>
+  <si>
+    <t>Prefabs/NPCs/NPC_Pilot</t>
+  </si>
+  <si>
+    <t>Portraits/Portrait_Pilot</t>
+  </si>
+  <si>
+    <t>char_creature</t>
+  </si>
+  <si>
+    <t>괴물</t>
+  </si>
+  <si>
+    <t>Prefabs/NPCs/NPC_Creature</t>
+  </si>
+  <si>
+    <t>Portraits/Creature_Portrait</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -112,6 +198,11 @@
     <font>
       <sz val="10"/>
       <color rgb="FF008000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -203,7 +294,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -223,16 +314,24 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -461,17 +560,23 @@
     <col min="4" max="4" width="27.5703125" style="2" customWidth="1"/>
     <col min="5" max="5" width="30.5703125" style="2" customWidth="1"/>
     <col min="6" max="6" width="26.5703125" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="12.5703125" style="2"/>
+    <col min="7" max="7" width="36.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="25.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="29" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="27.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="12.5703125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="12" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
@@ -480,80 +585,172 @@
       <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="2" spans="1:15" ht="12.75">
-      <c r="A2" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="14" t="s">
-        <v>6</v>
+      <c r="A2" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>12</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="3" spans="1:15" s="10" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A3" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="11"/>
+      <c r="A3" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="K3" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3" s="10" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="4" spans="1:15" ht="15.75" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>14</v>
+        <v>27</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>28</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="12"/>
-      <c r="G4" s="4"/>
+        <v>29</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>32</v>
+      </c>
       <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
+      <c r="I4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
     </row>
     <row r="5" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A5" s="3"/>
-      <c r="B5" s="5"/>
+      <c r="A5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>37</v>
+      </c>
       <c r="C5" s="5"/>
-      <c r="D5" s="4"/>
+      <c r="D5" s="4" t="s">
+        <v>38</v>
+      </c>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
+      <c r="I5" s="4" t="s">
+        <v>39</v>
+      </c>
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -562,15 +759,23 @@
       <c r="O5" s="4"/>
     </row>
     <row r="6" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
+      <c r="A6" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>41</v>
+      </c>
       <c r="C6" s="5"/>
-      <c r="D6" s="4"/>
+      <c r="D6" s="4" t="s">
+        <v>42</v>
+      </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
+      <c r="I6" s="4" t="s">
+        <v>43</v>
+      </c>
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
